--- a/docs/sheets/zzpaper2.xlsx
+++ b/docs/sheets/zzpaper2.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\1_PhD\Obsidian\Home\3. Writing\paperfire2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\docs\sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A887F4-B77D-4B02-92DD-47D115C411B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A724630-8864-4ADB-8BEB-DBC2FCA5DB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17010" yWindow="285" windowWidth="28110" windowHeight="16035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" r:id="rId1"/>
-    <sheet name="dataset" sheetId="5" r:id="rId2"/>
+    <sheet name="baseline_DFire" sheetId="9" r:id="rId1"/>
+    <sheet name="video_to_download" sheetId="8" r:id="rId2"/>
+    <sheet name="available_dataset" sheetId="7" r:id="rId3"/>
+    <sheet name="baseline" sheetId="1" r:id="rId4"/>
+    <sheet name="dataset" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -138,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="119">
   <si>
     <t>citekey</t>
   </si>
@@ -242,16 +246,278 @@
   <si>
     <t>vis</t>
   </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t># Videos</t>
+  </si>
+  <si>
+    <t>Resolution Min</t>
+  </si>
+  <si>
+    <t>Resolution Max</t>
+  </si>
+  <si>
+    <t>FireSmoke</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Indoor</t>
+  </si>
+  <si>
+    <t>Outdoor</t>
+  </si>
+  <si>
+    <t>Static camera</t>
+  </si>
+  <si>
+    <t>VisiFire Bilkent (Cetin, 0000)</t>
+  </si>
+  <si>
+    <t>320 x 240</t>
+  </si>
+  <si>
+    <t>720 x 576</t>
+  </si>
+  <si>
+    <t>D-Fire (de Venancio et al., 2021)</t>
+  </si>
+  <si>
+    <t>1280 x 720</t>
+  </si>
+  <si>
+    <t>KMU (Ko et al., 2011)</t>
+  </si>
+  <si>
+    <t>Mivia FIRE (Borgia et al., 2015)</t>
+  </si>
+  <si>
+    <t>800 x 600</t>
+  </si>
+  <si>
+    <t>Mivia SMOKE (Borgia et al., 2015)</t>
+  </si>
+  <si>
+    <t>292 x 240</t>
+  </si>
+  <si>
+    <t>USTC Smoke (in2017smoke)</t>
+  </si>
+  <si>
+    <t>1920 x 1080</t>
+  </si>
+  <si>
+    <t>Moving camera</t>
+  </si>
+  <si>
+    <t>FireNet (Lad et al., 2019)</t>
+  </si>
+  <si>
+    <t>352 x 222</t>
+  </si>
+  <si>
+    <t>FireSense (Kose et al., 2010)</t>
+  </si>
+  <si>
+    <t>300 x 240</t>
+  </si>
+  <si>
+    <t>1600 x 1200</t>
+  </si>
+  <si>
+    <t>FiSmo (Cazzato et al., 2020)</t>
+  </si>
+  <si>
+    <t>FURG (Steffens et al., 2015)</t>
+  </si>
+  <si>
+    <t>240 x 344</t>
+  </si>
+  <si>
+    <t>Mix camera</t>
+  </si>
+  <si>
+    <t>VSD3 (Huang et al., 2022)</t>
+  </si>
+  <si>
+    <t>352 x 288</t>
+  </si>
+  <si>
+    <t>2048 x 1536</t>
+  </si>
+  <si>
+    <t>Static Camera</t>
+  </si>
+  <si>
+    <t>Ours (2025)</t>
+  </si>
+  <si>
+    <t>peng2025yolo (https://github.com/PengBo0/Home-fire-dataset/tree/main)</t>
+  </si>
+  <si>
+    <t>aihub (https://aihub.or.kr/aihubdata/data/view.do?dataSetSn=71751)</t>
+  </si>
+  <si>
+    <t>https://pixabay.com/zh/videos/christmas-tree-fireplace-twinkle-100317/</t>
+  </si>
+  <si>
+    <t>https://pixabay.com/zh/videos/background-room-dark-fireplace-136334/</t>
+  </si>
+  <si>
+    <t>https://pixabay.com/zh/videos/chef-cook-cooking-hibachi-show-174220/</t>
+  </si>
+  <si>
+    <t>https://pixabay.com/zh/videos/incense-burner-smoke-spiritual-200929/</t>
+  </si>
+  <si>
+    <t>https://pixabay.com/zh/videos/fireplace-living-room-cozy-room-146947/</t>
+  </si>
+  <si>
+    <t>https://www.pexels.com/zh-cn/video/11048627/</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=YZFMrfjgYqc</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LOn61NlogYQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=HYvMWIvghnQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=DoSxKZzT2i0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Doyg3QJVXzA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0u5jCPHmevE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8nz5ijXcckI</t>
+  </si>
+  <si>
+    <t>https://www.bilibili.com/video/BV1NB4y1R7J7/?spm_id_from=333.999.0.0&amp;vd_source=a6d4a6b8e3b03c62363dc58d6a2f8a59</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=oEINd6SYZJs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=sEUTJ3p4sjM</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=O9oB2nOr7L4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BjbfJqXLMmY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SgbSKwTdaNs</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=01w0cOzmCvc</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=EehF0UHYaYk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JGIICiX2CNI</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@sprinklersafe</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yvY4u_wvXi4</t>
+  </si>
+  <si>
+    <t>DaniDeniz/IndoorActionDataset: Indoor Action Dataset, this dataset includes daily life activities in indoor scenarios recorded in videos.</t>
+  </si>
+  <si>
+    <t>https://www.mpi-inf.mpg.de/de/departments/computer-vision-and-machine-learning/research/human-activity-recognition/mpii-cooking-2-dataset</t>
+  </si>
+  <si>
+    <t>MobileNet [5]</t>
+  </si>
+  <si>
+    <t>[3]</t>
+  </si>
+  <si>
+    <t>FireNet(*) [3]</t>
+  </si>
+  <si>
+    <t>YOLOv5l+AVT</t>
+  </si>
+  <si>
+    <t>YOLOv5l+TPT</t>
+  </si>
+  <si>
+    <t>YOLOv5l</t>
+  </si>
+  <si>
+    <t>YOLOv5s+AVT</t>
+  </si>
+  <si>
+    <t>YOLOv5s+TPT</t>
+  </si>
+  <si>
+    <t>YOLOv5s</t>
+  </si>
+  <si>
+    <t>[20]</t>
+  </si>
+  <si>
+    <t>FireNet [3]</t>
+  </si>
+  <si>
+    <t>FPS</t>
+  </si>
+  <si>
+    <t>TNR (%)</t>
+  </si>
+  <si>
+    <t>FNR (%)</t>
+  </si>
+  <si>
+    <t>FPR (%)</t>
+  </si>
+  <si>
+    <t>TPR (%)</t>
+  </si>
+  <si>
+    <t>F1-score</t>
+  </si>
+  <si>
+    <t>Accuracy (%)</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Video database</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -305,8 +571,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -319,8 +593,14 @@
         <bgColor rgb="FF999999"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -343,44 +623,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{7317EE94-6EA5-49B6-9EB3-3A1D4149183D}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{A9F65691-4FC3-4A70-9633-38E217A6D207}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -701,6 +1004,1100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DECC613-DEAA-47C9-A408-516F751E59A8}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="13">
+        <v>68.569999999999993</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.76</v>
+      </c>
+      <c r="E2" s="13">
+        <v>97.14</v>
+      </c>
+      <c r="F2" s="13">
+        <v>60</v>
+      </c>
+      <c r="G2" s="13">
+        <v>2.86</v>
+      </c>
+      <c r="H2" s="13">
+        <v>40</v>
+      </c>
+      <c r="I2" s="13">
+        <v>162.27000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="13">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="D3" s="13">
+        <v>0.76</v>
+      </c>
+      <c r="E3" s="13">
+        <v>91.43</v>
+      </c>
+      <c r="F3" s="13">
+        <v>48.57</v>
+      </c>
+      <c r="G3" s="13">
+        <v>8.57</v>
+      </c>
+      <c r="H3" s="13">
+        <v>51.43</v>
+      </c>
+      <c r="I3" s="13">
+        <v>162.81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="13">
+        <v>72.86</v>
+      </c>
+      <c r="D4" s="13">
+        <v>0.78</v>
+      </c>
+      <c r="E4" s="13">
+        <v>97.14</v>
+      </c>
+      <c r="F4" s="13">
+        <v>51.43</v>
+      </c>
+      <c r="G4" s="13">
+        <v>2.86</v>
+      </c>
+      <c r="H4" s="13">
+        <v>48.57</v>
+      </c>
+      <c r="I4" s="13">
+        <v>159.65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="13">
+        <v>60</v>
+      </c>
+      <c r="D5" s="13">
+        <v>0.71</v>
+      </c>
+      <c r="E5" s="13">
+        <v>100</v>
+      </c>
+      <c r="F5" s="13">
+        <v>80</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0</v>
+      </c>
+      <c r="H5" s="13">
+        <v>20</v>
+      </c>
+      <c r="I5" s="13">
+        <v>59.34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="13">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="D6" s="13">
+        <v>0.77</v>
+      </c>
+      <c r="E6" s="13">
+        <v>97.14</v>
+      </c>
+      <c r="F6" s="13">
+        <v>54.29</v>
+      </c>
+      <c r="G6" s="13">
+        <v>2.86</v>
+      </c>
+      <c r="H6" s="13">
+        <v>45.71</v>
+      </c>
+      <c r="I6" s="13">
+        <v>59.36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="13">
+        <v>65.709999999999994</v>
+      </c>
+      <c r="D7" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="E7" s="13">
+        <v>100</v>
+      </c>
+      <c r="F7" s="13">
+        <v>68.569999999999993</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
+        <v>31.43</v>
+      </c>
+      <c r="I7" s="13">
+        <v>59.44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="13">
+        <v>54</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="13">
+        <v>46</v>
+      </c>
+      <c r="F8" s="13">
+        <v>38</v>
+      </c>
+      <c r="G8" s="13">
+        <v>54</v>
+      </c>
+      <c r="H8" s="13">
+        <v>62</v>
+      </c>
+      <c r="I8" s="13">
+        <v>32.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="13">
+        <v>35</v>
+      </c>
+      <c r="D9" s="13">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13">
+        <v>30</v>
+      </c>
+      <c r="G9" s="13">
+        <v>100</v>
+      </c>
+      <c r="H9" s="13">
+        <v>70</v>
+      </c>
+      <c r="I9" s="13">
+        <v>23.66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="13">
+        <v>91.94</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0.95</v>
+      </c>
+      <c r="E10" s="13">
+        <v>100</v>
+      </c>
+      <c r="F10" s="13">
+        <v>31.25</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13">
+        <v>68.75</v>
+      </c>
+      <c r="I10" s="13">
+        <v>138.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="13">
+        <v>95.16</v>
+      </c>
+      <c r="D11" s="13">
+        <v>0.97</v>
+      </c>
+      <c r="E11" s="13">
+        <v>97.83</v>
+      </c>
+      <c r="F11" s="13">
+        <v>12.5</v>
+      </c>
+      <c r="G11" s="13">
+        <v>2.17</v>
+      </c>
+      <c r="H11" s="13">
+        <v>87.5</v>
+      </c>
+      <c r="I11" s="13">
+        <v>137.74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="13">
+        <v>90.32</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0.94</v>
+      </c>
+      <c r="E12" s="13">
+        <v>95.65</v>
+      </c>
+      <c r="F12" s="13">
+        <v>25</v>
+      </c>
+      <c r="G12" s="13">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H12" s="13">
+        <v>75</v>
+      </c>
+      <c r="I12" s="13">
+        <v>138.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="13">
+        <v>93.55</v>
+      </c>
+      <c r="D13" s="13">
+        <v>0.96</v>
+      </c>
+      <c r="E13" s="13">
+        <v>100</v>
+      </c>
+      <c r="F13" s="13">
+        <v>25</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
+        <v>75</v>
+      </c>
+      <c r="I13" s="13">
+        <v>55.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="13">
+        <v>95.16</v>
+      </c>
+      <c r="D14" s="13">
+        <v>0.97</v>
+      </c>
+      <c r="E14" s="13">
+        <v>97.83</v>
+      </c>
+      <c r="F14" s="13">
+        <v>12.5</v>
+      </c>
+      <c r="G14" s="13">
+        <v>2.17</v>
+      </c>
+      <c r="H14" s="13">
+        <v>87.5</v>
+      </c>
+      <c r="I14" s="13">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="13">
+        <v>93.55</v>
+      </c>
+      <c r="D15" s="13">
+        <v>0.96</v>
+      </c>
+      <c r="E15" s="13">
+        <v>97.83</v>
+      </c>
+      <c r="F15" s="13">
+        <v>18.75</v>
+      </c>
+      <c r="G15" s="13">
+        <v>2.17</v>
+      </c>
+      <c r="H15" s="13">
+        <v>81.25</v>
+      </c>
+      <c r="I15" s="13">
+        <v>55.29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="13">
+        <v>87.1</v>
+      </c>
+      <c r="D16" s="13">
+        <v>0.92</v>
+      </c>
+      <c r="E16" s="13">
+        <v>95.65</v>
+      </c>
+      <c r="F16" s="13">
+        <v>37.5</v>
+      </c>
+      <c r="G16" s="13">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H16" s="13">
+        <v>62.5</v>
+      </c>
+      <c r="I16" s="13">
+        <v>32.909999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="13">
+        <v>93.55</v>
+      </c>
+      <c r="D17" s="13">
+        <v>0.96</v>
+      </c>
+      <c r="E17" s="13">
+        <v>95.65</v>
+      </c>
+      <c r="F17" s="13">
+        <v>12.5</v>
+      </c>
+      <c r="G17" s="13">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H17" s="13">
+        <v>87.5</v>
+      </c>
+      <c r="I17" s="13">
+        <v>27.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA50FCC2-008E-4DCD-A42A-91812C3A7681}">
+  <dimension ref="A1:A28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="135" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{E03E7DF8-5062-435C-8459-A33415F969DF}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{4EF25A75-FC98-467D-B59C-E881D68A3506}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{8405E644-1F1A-4D6E-94ED-CA65FDE83E5F}"/>
+    <hyperlink ref="A6" r:id="rId4" xr:uid="{FE6DA5F5-91C4-401B-96BD-490AF3F20D1E}"/>
+    <hyperlink ref="A7" r:id="rId5" xr:uid="{90952ACE-C304-4A08-AA8F-BD4BF9C6528F}"/>
+    <hyperlink ref="A8" r:id="rId6" xr:uid="{3DA5D497-9783-45D6-881D-6C8CE5B43E4E}"/>
+    <hyperlink ref="A9" r:id="rId7" xr:uid="{3DC5EB29-8B9C-410E-84EE-3FCAFCFF6387}"/>
+    <hyperlink ref="A10" r:id="rId8" xr:uid="{C0538FA3-4645-4570-9750-BF98D3395E6B}"/>
+    <hyperlink ref="A11" r:id="rId9" xr:uid="{50B28E52-793C-4E4D-B672-7FA955BA17A0}"/>
+    <hyperlink ref="A12" r:id="rId10" xr:uid="{E99DB158-52F3-4215-8A2B-87E1D67EF8B5}"/>
+    <hyperlink ref="A13" r:id="rId11" xr:uid="{268F9046-3705-4533-B965-B634B4B73760}"/>
+    <hyperlink ref="A14" r:id="rId12" xr:uid="{77D14C67-285E-45A4-A50A-EE0BC4323BCB}"/>
+    <hyperlink ref="A15" r:id="rId13" xr:uid="{166EE997-8D27-4655-9E11-142BA1996A5D}"/>
+    <hyperlink ref="A16" r:id="rId14" xr:uid="{6981F779-2D64-4FE0-BB55-846B8AFA96A2}"/>
+    <hyperlink ref="A17" r:id="rId15" xr:uid="{B85E1B41-BCC8-41AD-BDCB-7A6575EE5326}"/>
+    <hyperlink ref="A18" r:id="rId16" xr:uid="{B5D9CE71-A8BF-463E-9568-99A58615F8C7}"/>
+    <hyperlink ref="A19" r:id="rId17" xr:uid="{39E621E7-4D66-4C10-81FB-B9378EA2EA9B}"/>
+    <hyperlink ref="A20" r:id="rId18" xr:uid="{56B5AA02-ACC3-46F4-AB6F-7671FF1DD817}"/>
+    <hyperlink ref="A21" r:id="rId19" xr:uid="{78089178-BBC9-4399-B8F9-D0334703F54D}"/>
+    <hyperlink ref="A22" r:id="rId20" xr:uid="{A4DB2E8E-CE20-424B-B768-57F7A34C1D42}"/>
+    <hyperlink ref="A23" r:id="rId21" xr:uid="{9CFBDD8E-AECE-48C5-BAD5-D0D063BE0A5C}"/>
+    <hyperlink ref="A24" r:id="rId22" xr:uid="{DDE11943-A8B6-4D87-AC4A-FEA3AA41D0B3}"/>
+    <hyperlink ref="A25" r:id="rId23" xr:uid="{0342C5C7-6453-4DF5-9E88-E3186022B840}"/>
+    <hyperlink ref="A26" r:id="rId24" xr:uid="{F8719220-CB59-4AF7-8490-9131D9B872C2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE53349C-5F79-484F-8923-74257D605F4E}">
+  <dimension ref="B2:J17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="13"/>
+    <col min="2" max="2" width="14.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="14">
+        <v>39</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="14">
+        <v>38</v>
+      </c>
+      <c r="H3" s="14">
+        <v>1</v>
+      </c>
+      <c r="I3" s="14">
+        <v>6</v>
+      </c>
+      <c r="J3" s="14">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="14">
+        <v>100</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="14">
+        <v>50</v>
+      </c>
+      <c r="H4" s="14">
+        <v>50</v>
+      </c>
+      <c r="I4" s="14">
+        <v>0</v>
+      </c>
+      <c r="J4" s="14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="14">
+        <v>38</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="14">
+        <v>28</v>
+      </c>
+      <c r="H5" s="14">
+        <v>10</v>
+      </c>
+      <c r="I5" s="14">
+        <v>10</v>
+      </c>
+      <c r="J5" s="14">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="14">
+        <v>31</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="14">
+        <v>28</v>
+      </c>
+      <c r="H6" s="14">
+        <v>3</v>
+      </c>
+      <c r="I6" s="14">
+        <v>4</v>
+      </c>
+      <c r="J6" s="14">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="14">
+        <v>149</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="14">
+        <v>76</v>
+      </c>
+      <c r="H7" s="14">
+        <v>73</v>
+      </c>
+      <c r="I7" s="14">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="14">
+        <v>30</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="14">
+        <v>22</v>
+      </c>
+      <c r="H8" s="14">
+        <v>8</v>
+      </c>
+      <c r="I8" s="14">
+        <v>30</v>
+      </c>
+      <c r="J8" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="14">
+        <v>62</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="14">
+        <v>46</v>
+      </c>
+      <c r="H10" s="14">
+        <v>16</v>
+      </c>
+      <c r="I10" s="14">
+        <v>30</v>
+      </c>
+      <c r="J10" s="14">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="14">
+        <v>49</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="14">
+        <v>24</v>
+      </c>
+      <c r="H11" s="14">
+        <v>25</v>
+      </c>
+      <c r="I11" s="14">
+        <v>10</v>
+      </c>
+      <c r="J11" s="14">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="14">
+        <v>88</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="14">
+        <v>80</v>
+      </c>
+      <c r="H12" s="14">
+        <v>8</v>
+      </c>
+      <c r="I12" s="14">
+        <v>0</v>
+      </c>
+      <c r="J12" s="14">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="14">
+        <v>22</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="14">
+        <v>17</v>
+      </c>
+      <c r="H13" s="14">
+        <v>5</v>
+      </c>
+      <c r="I13" s="14">
+        <v>3</v>
+      </c>
+      <c r="J13" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="14">
+        <v>20</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="14">
+        <v>8</v>
+      </c>
+      <c r="H15" s="14">
+        <v>12</v>
+      </c>
+      <c r="I15" s="14">
+        <v>6</v>
+      </c>
+      <c r="J15" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z999"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -28755,7 +30152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -29787,4 +31184,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E79F85D-0A90-4BD9-B6A4-D426E9009D4C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/sheets/zzpaper2.xlsx
+++ b/docs/sheets/zzpaper2.xlsx
@@ -8,17 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\docs\sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A724630-8864-4ADB-8BEB-DBC2FCA5DB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7833753-BED3-48C4-A582-11160277A5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline_DFire" sheetId="9" r:id="rId1"/>
-    <sheet name="video_to_download" sheetId="8" r:id="rId2"/>
-    <sheet name="available_dataset" sheetId="7" r:id="rId3"/>
-    <sheet name="baseline" sheetId="1" r:id="rId4"/>
-    <sheet name="dataset" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
+    <sheet name="dataset" sheetId="7" r:id="rId1"/>
+    <sheet name="baseline" sheetId="1" r:id="rId2"/>
+    <sheet name="idea_list" sheetId="10" r:id="rId3"/>
+    <sheet name="perf_DFire" sheetId="9" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -142,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="150">
   <si>
     <t>citekey</t>
   </si>
@@ -501,16 +499,193 @@
   <si>
     <t>Video database</t>
   </si>
+  <si>
+    <t>3840 x 2160 (most 1920x1080)</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>main idea</t>
+  </si>
+  <si>
+    <t>feature type</t>
+  </si>
+  <si>
+    <t>Fire detection using statistical color model in video sequences</t>
+  </si>
+  <si>
+    <t>motion map &amp; fire-mask =&gt; region of fire =&gt; analyze change in fire areas</t>
+  </si>
+  <si>
+    <t>color: rule for fire pixel</t>
+  </si>
+  <si>
+    <t>Fire detection based on vision sensor and support vector machines</t>
+  </si>
+  <si>
+    <t>fire color detection + moving pixel + Non-fire pixel removal using temporal luminance variation</t>
+  </si>
+  <si>
+    <t>Fire detection in video sequences using a generic color model</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">flame pixels but in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>YCbCr color space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (better than RGB)</t>
+    </r>
+  </si>
+  <si>
+    <t>Fast and Efficient Method for Fire Detection Using Image Processing</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">flame pixels in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CIE L*a*b* color channels</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + moving pixel detection; changes in number of fire pixel</t>
+    </r>
+  </si>
+  <si>
+    <t>Multi-feature fusion based fast video flame detection</t>
+  </si>
+  <si>
+    <t>flame flicker (brightness change)</t>
+  </si>
+  <si>
+    <t>Fire Detection in Video Using LMS Based Active Learning</t>
+  </si>
+  <si>
+    <t>Temporal Wavelet Analysis (change in time); Spatial Wavelet Analysis (change in texture)</t>
+  </si>
+  <si>
+    <t>A fast accumulative motion orientation model based on integral image for video smoke detection</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fast motion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> estimation; block base; ==&gt; for smoke only</t>
+    </r>
+  </si>
+  <si>
+    <t>Fire and smoke detection without sensors: Image processing based approach</t>
+  </si>
+  <si>
+    <t>fire + smoke color rules</t>
+  </si>
+  <si>
+    <t>A Study of Rule-based Flame Pixel Classifiers in
+Still Images</t>
+  </si>
+  <si>
+    <t>Fire Detection Methods Based on Various Color Spaces
+and Gaussian Mixture Models</t>
+  </si>
+  <si>
+    <t>A Computer Vision-Based Method
+for Fire Detection in Color Videos</t>
+  </si>
+  <si>
+    <t>An Early Flame Detection System Based on Image
+Block Threshold Selection Using Knowledge of
+Local and Global Feature Analysis</t>
+  </si>
+  <si>
+    <t>A survey on vision-based outdoor smoke detection techniques for
+environmental safety</t>
+  </si>
+  <si>
+    <t>A fast accumulative motion orientation model based on integral
+image for video smoke detection</t>
+  </si>
+  <si>
+    <t>block</t>
+  </si>
+  <si>
+    <t>Automatic fire pixel detection using image processing: a comparative analysis of rule-based and machine learning-based methods</t>
+  </si>
+  <si>
+    <t>rule-based</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -639,51 +814,68 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{7317EE94-6EA5-49B6-9EB3-3A1D4149183D}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{A9F65691-4FC3-4A70-9633-38E217A6D207}"/>
+    <cellStyle name="Normal 3" xfId="4" xr:uid="{15BA3769-005B-4CDF-B761-EEA81D658B44}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -696,6 +888,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>5229225</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>513693</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>37479</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94BE3CFB-163E-43D7-B412-BF7852DBDA95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11877675" y="6496050"/>
+          <a:ext cx="5257143" cy="4971429"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>4971349</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>160782</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C924333-C704-4AD4-B8ED-B0E8A70C6954}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6010275" y="6638925"/>
+          <a:ext cx="5609524" cy="9142857"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1004,694 +1289,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DECC613-DEAA-47C9-A408-516F751E59A8}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="9.140625" style="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="13">
-        <v>68.569999999999993</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.76</v>
-      </c>
-      <c r="E2" s="13">
-        <v>97.14</v>
-      </c>
-      <c r="F2" s="13">
-        <v>60</v>
-      </c>
-      <c r="G2" s="13">
-        <v>2.86</v>
-      </c>
-      <c r="H2" s="13">
-        <v>40</v>
-      </c>
-      <c r="I2" s="13">
-        <v>162.27000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="13">
-        <v>71.430000000000007</v>
-      </c>
-      <c r="D3" s="13">
-        <v>0.76</v>
-      </c>
-      <c r="E3" s="13">
-        <v>91.43</v>
-      </c>
-      <c r="F3" s="13">
-        <v>48.57</v>
-      </c>
-      <c r="G3" s="13">
-        <v>8.57</v>
-      </c>
-      <c r="H3" s="13">
-        <v>51.43</v>
-      </c>
-      <c r="I3" s="13">
-        <v>162.81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="13">
-        <v>72.86</v>
-      </c>
-      <c r="D4" s="13">
-        <v>0.78</v>
-      </c>
-      <c r="E4" s="13">
-        <v>97.14</v>
-      </c>
-      <c r="F4" s="13">
-        <v>51.43</v>
-      </c>
-      <c r="G4" s="13">
-        <v>2.86</v>
-      </c>
-      <c r="H4" s="13">
-        <v>48.57</v>
-      </c>
-      <c r="I4" s="13">
-        <v>159.65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="13">
-        <v>60</v>
-      </c>
-      <c r="D5" s="13">
-        <v>0.71</v>
-      </c>
-      <c r="E5" s="13">
-        <v>100</v>
-      </c>
-      <c r="F5" s="13">
-        <v>80</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13">
-        <v>20</v>
-      </c>
-      <c r="I5" s="13">
-        <v>59.34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="13">
-        <v>71.430000000000007</v>
-      </c>
-      <c r="D6" s="13">
-        <v>0.77</v>
-      </c>
-      <c r="E6" s="13">
-        <v>97.14</v>
-      </c>
-      <c r="F6" s="13">
-        <v>54.29</v>
-      </c>
-      <c r="G6" s="13">
-        <v>2.86</v>
-      </c>
-      <c r="H6" s="13">
-        <v>45.71</v>
-      </c>
-      <c r="I6" s="13">
-        <v>59.36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="13">
-        <v>65.709999999999994</v>
-      </c>
-      <c r="D7" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="E7" s="13">
-        <v>100</v>
-      </c>
-      <c r="F7" s="13">
-        <v>68.569999999999993</v>
-      </c>
-      <c r="G7" s="13">
-        <v>0</v>
-      </c>
-      <c r="H7" s="13">
-        <v>31.43</v>
-      </c>
-      <c r="I7" s="13">
-        <v>59.44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="13">
-        <v>54</v>
-      </c>
-      <c r="D8" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="13">
-        <v>46</v>
-      </c>
-      <c r="F8" s="13">
-        <v>38</v>
-      </c>
-      <c r="G8" s="13">
-        <v>54</v>
-      </c>
-      <c r="H8" s="13">
-        <v>62</v>
-      </c>
-      <c r="I8" s="13">
-        <v>32.06</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="13">
-        <v>35</v>
-      </c>
-      <c r="D9" s="13">
-        <v>0</v>
-      </c>
-      <c r="E9" s="13">
-        <v>0</v>
-      </c>
-      <c r="F9" s="13">
-        <v>30</v>
-      </c>
-      <c r="G9" s="13">
-        <v>100</v>
-      </c>
-      <c r="H9" s="13">
-        <v>70</v>
-      </c>
-      <c r="I9" s="13">
-        <v>23.66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="13">
-        <v>91.94</v>
-      </c>
-      <c r="D10" s="13">
-        <v>0.95</v>
-      </c>
-      <c r="E10" s="13">
-        <v>100</v>
-      </c>
-      <c r="F10" s="13">
-        <v>31.25</v>
-      </c>
-      <c r="G10" s="13">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13">
-        <v>68.75</v>
-      </c>
-      <c r="I10" s="13">
-        <v>138.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11" s="13">
-        <v>95.16</v>
-      </c>
-      <c r="D11" s="13">
-        <v>0.97</v>
-      </c>
-      <c r="E11" s="13">
-        <v>97.83</v>
-      </c>
-      <c r="F11" s="13">
-        <v>12.5</v>
-      </c>
-      <c r="G11" s="13">
-        <v>2.17</v>
-      </c>
-      <c r="H11" s="13">
-        <v>87.5</v>
-      </c>
-      <c r="I11" s="13">
-        <v>137.74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="13">
-        <v>90.32</v>
-      </c>
-      <c r="D12" s="13">
-        <v>0.94</v>
-      </c>
-      <c r="E12" s="13">
-        <v>95.65</v>
-      </c>
-      <c r="F12" s="13">
-        <v>25</v>
-      </c>
-      <c r="G12" s="13">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="H12" s="13">
-        <v>75</v>
-      </c>
-      <c r="I12" s="13">
-        <v>138.22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="13">
-        <v>93.55</v>
-      </c>
-      <c r="D13" s="13">
-        <v>0.96</v>
-      </c>
-      <c r="E13" s="13">
-        <v>100</v>
-      </c>
-      <c r="F13" s="13">
-        <v>25</v>
-      </c>
-      <c r="G13" s="13">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13">
-        <v>75</v>
-      </c>
-      <c r="I13" s="13">
-        <v>55.85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="13">
-        <v>95.16</v>
-      </c>
-      <c r="D14" s="13">
-        <v>0.97</v>
-      </c>
-      <c r="E14" s="13">
-        <v>97.83</v>
-      </c>
-      <c r="F14" s="13">
-        <v>12.5</v>
-      </c>
-      <c r="G14" s="13">
-        <v>2.17</v>
-      </c>
-      <c r="H14" s="13">
-        <v>87.5</v>
-      </c>
-      <c r="I14" s="13">
-        <v>55.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="13">
-        <v>93.55</v>
-      </c>
-      <c r="D15" s="13">
-        <v>0.96</v>
-      </c>
-      <c r="E15" s="13">
-        <v>97.83</v>
-      </c>
-      <c r="F15" s="13">
-        <v>18.75</v>
-      </c>
-      <c r="G15" s="13">
-        <v>2.17</v>
-      </c>
-      <c r="H15" s="13">
-        <v>81.25</v>
-      </c>
-      <c r="I15" s="13">
-        <v>55.29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="13">
-        <v>87.1</v>
-      </c>
-      <c r="D16" s="13">
-        <v>0.92</v>
-      </c>
-      <c r="E16" s="13">
-        <v>95.65</v>
-      </c>
-      <c r="F16" s="13">
-        <v>37.5</v>
-      </c>
-      <c r="G16" s="13">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="H16" s="13">
-        <v>62.5</v>
-      </c>
-      <c r="I16" s="13">
-        <v>32.909999999999997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="13">
-        <v>93.55</v>
-      </c>
-      <c r="D17" s="13">
-        <v>0.96</v>
-      </c>
-      <c r="E17" s="13">
-        <v>95.65</v>
-      </c>
-      <c r="F17" s="13">
-        <v>12.5</v>
-      </c>
-      <c r="G17" s="13">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="H17" s="13">
-        <v>87.5</v>
-      </c>
-      <c r="I17" s="13">
-        <v>27.9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA50FCC2-008E-4DCD-A42A-91812C3A7681}">
-  <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="135" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{E03E7DF8-5062-435C-8459-A33415F969DF}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{4EF25A75-FC98-467D-B59C-E881D68A3506}"/>
-    <hyperlink ref="A5" r:id="rId3" xr:uid="{8405E644-1F1A-4D6E-94ED-CA65FDE83E5F}"/>
-    <hyperlink ref="A6" r:id="rId4" xr:uid="{FE6DA5F5-91C4-401B-96BD-490AF3F20D1E}"/>
-    <hyperlink ref="A7" r:id="rId5" xr:uid="{90952ACE-C304-4A08-AA8F-BD4BF9C6528F}"/>
-    <hyperlink ref="A8" r:id="rId6" xr:uid="{3DA5D497-9783-45D6-881D-6C8CE5B43E4E}"/>
-    <hyperlink ref="A9" r:id="rId7" xr:uid="{3DC5EB29-8B9C-410E-84EE-3FCAFCFF6387}"/>
-    <hyperlink ref="A10" r:id="rId8" xr:uid="{C0538FA3-4645-4570-9750-BF98D3395E6B}"/>
-    <hyperlink ref="A11" r:id="rId9" xr:uid="{50B28E52-793C-4E4D-B672-7FA955BA17A0}"/>
-    <hyperlink ref="A12" r:id="rId10" xr:uid="{E99DB158-52F3-4215-8A2B-87E1D67EF8B5}"/>
-    <hyperlink ref="A13" r:id="rId11" xr:uid="{268F9046-3705-4533-B965-B634B4B73760}"/>
-    <hyperlink ref="A14" r:id="rId12" xr:uid="{77D14C67-285E-45A4-A50A-EE0BC4323BCB}"/>
-    <hyperlink ref="A15" r:id="rId13" xr:uid="{166EE997-8D27-4655-9E11-142BA1996A5D}"/>
-    <hyperlink ref="A16" r:id="rId14" xr:uid="{6981F779-2D64-4FE0-BB55-846B8AFA96A2}"/>
-    <hyperlink ref="A17" r:id="rId15" xr:uid="{B85E1B41-BCC8-41AD-BDCB-7A6575EE5326}"/>
-    <hyperlink ref="A18" r:id="rId16" xr:uid="{B5D9CE71-A8BF-463E-9568-99A58615F8C7}"/>
-    <hyperlink ref="A19" r:id="rId17" xr:uid="{39E621E7-4D66-4C10-81FB-B9378EA2EA9B}"/>
-    <hyperlink ref="A20" r:id="rId18" xr:uid="{56B5AA02-ACC3-46F4-AB6F-7671FF1DD817}"/>
-    <hyperlink ref="A21" r:id="rId19" xr:uid="{78089178-BBC9-4399-B8F9-D0334703F54D}"/>
-    <hyperlink ref="A22" r:id="rId20" xr:uid="{A4DB2E8E-CE20-424B-B768-57F7A34C1D42}"/>
-    <hyperlink ref="A23" r:id="rId21" xr:uid="{9CFBDD8E-AECE-48C5-BAD5-D0D063BE0A5C}"/>
-    <hyperlink ref="A24" r:id="rId22" xr:uid="{DDE11943-A8B6-4D87-AC4A-FEA3AA41D0B3}"/>
-    <hyperlink ref="A25" r:id="rId23" xr:uid="{0342C5C7-6453-4DF5-9E88-E3186022B840}"/>
-    <hyperlink ref="A26" r:id="rId24" xr:uid="{F8719220-CB59-4AF7-8490-9131D9B872C2}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE53349C-5F79-484F-8923-74257D605F4E}">
-  <dimension ref="B2:J17"/>
+  <dimension ref="B2:W35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="13"/>
@@ -1699,7 +1298,7 @@
     <col min="3" max="3" width="30.28515625" style="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.85546875" style="13" customWidth="1"/>
     <col min="7" max="7" width="10.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.85546875" style="13" bestFit="1" customWidth="1"/>
@@ -1707,7 +1306,7 @@
     <col min="11" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="12" t="s">
         <v>34</v>
       </c>
@@ -1735,8 +1334,11 @@
       <c r="J2" s="12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M2" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="14" t="s">
         <v>43</v>
       </c>
@@ -1764,8 +1366,11 @@
       <c r="J3" s="14">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M3" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
         <v>43</v>
       </c>
@@ -1793,8 +1398,11 @@
       <c r="J4" s="14">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M4" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>43</v>
       </c>
@@ -1822,8 +1430,11 @@
       <c r="J5" s="14">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M5" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="14" t="s">
         <v>43</v>
       </c>
@@ -1851,8 +1462,11 @@
       <c r="J6" s="14">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M6" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>43</v>
       </c>
@@ -1880,8 +1494,11 @@
       <c r="J7" s="14">
         <v>149</v>
       </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M7" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
         <v>43</v>
       </c>
@@ -1909,8 +1526,11 @@
       <c r="J8" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M8" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -1920,8 +1540,11 @@
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M9" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>56</v>
       </c>
@@ -1949,8 +1572,11 @@
       <c r="J10" s="14">
         <v>32</v>
       </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M10" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>56</v>
       </c>
@@ -1978,8 +1604,11 @@
       <c r="J11" s="14">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M11" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="14" t="s">
         <v>56</v>
       </c>
@@ -2007,8 +1636,11 @@
       <c r="J12" s="14">
         <v>88</v>
       </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M12" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>56</v>
       </c>
@@ -2036,8 +1668,11 @@
       <c r="J13" s="14">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M13" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -2047,8 +1682,11 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M14" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
         <v>65</v>
       </c>
@@ -2076,8 +1714,25 @@
       <c r="J15" s="14">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="M15" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="M16" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
         <v>69</v>
       </c>
@@ -2085,19 +1740,204 @@
         <v>70</v>
       </c>
       <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
+      <c r="E17" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="14">
+        <v>75</v>
+      </c>
+      <c r="H17" s="14">
+        <v>75</v>
+      </c>
+      <c r="I17" s="14">
+        <v>150</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M18" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M19" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M20" s="15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M21" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M22" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M23" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M24" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M25" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M26" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M27" s="15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M28" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M29" s="13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M31" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
+      <c r="R31"/>
+      <c r="S31"/>
+      <c r="T31"/>
+      <c r="U31"/>
+      <c r="V31"/>
+      <c r="W31"/>
+    </row>
+    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="M32" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
+      <c r="R32"/>
+      <c r="S32"/>
+      <c r="T32"/>
+      <c r="U32"/>
+      <c r="V32"/>
+      <c r="W32"/>
+    </row>
+    <row r="33" spans="13:23" x14ac:dyDescent="0.25">
+      <c r="M33" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O33"/>
+      <c r="P33"/>
+      <c r="Q33"/>
+      <c r="R33"/>
+      <c r="S33"/>
+      <c r="T33"/>
+      <c r="U33"/>
+      <c r="V33"/>
+      <c r="W33"/>
+    </row>
+    <row r="34" spans="13:23" x14ac:dyDescent="0.25">
+      <c r="M34" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
+      <c r="R34"/>
+      <c r="S34"/>
+      <c r="T34"/>
+      <c r="U34"/>
+      <c r="V34"/>
+      <c r="W34"/>
+    </row>
+    <row r="35" spans="13:23" x14ac:dyDescent="0.25">
+      <c r="M35"/>
+      <c r="N35" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O35"/>
+      <c r="P35"/>
+      <c r="Q35"/>
+      <c r="R35"/>
+      <c r="S35"/>
+      <c r="T35"/>
+      <c r="U35"/>
+      <c r="V35"/>
+      <c r="W35"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="M4" r:id="rId1" xr:uid="{81F7E9A9-9B33-42B6-B7F0-327B6F0BD4FA}"/>
+    <hyperlink ref="M5" r:id="rId2" xr:uid="{BA7E36B9-D702-44C0-87D4-DD40DEE924F4}"/>
+    <hyperlink ref="M6" r:id="rId3" xr:uid="{FA65BFFC-92FC-410F-9965-01AD9B5A0575}"/>
+    <hyperlink ref="M7" r:id="rId4" xr:uid="{2204810E-B860-4C0F-8DCB-AC732FE7A057}"/>
+    <hyperlink ref="M8" r:id="rId5" xr:uid="{DB0D40FA-84DA-43D6-B39B-43EA9ACCBA1F}"/>
+    <hyperlink ref="M9" r:id="rId6" xr:uid="{497367EA-345D-41F0-9E08-C3C770F16825}"/>
+    <hyperlink ref="M10" r:id="rId7" xr:uid="{C8A30BA1-61B5-4061-A16A-50423DB0963C}"/>
+    <hyperlink ref="M11" r:id="rId8" xr:uid="{8412B789-F2F5-4BD1-83C8-AEDF90CDD659}"/>
+    <hyperlink ref="M12" r:id="rId9" xr:uid="{845565C4-CC18-4795-B910-78D11BC0C66B}"/>
+    <hyperlink ref="M13" r:id="rId10" xr:uid="{16272A60-409A-48FA-9A2F-268D6E78ADF9}"/>
+    <hyperlink ref="M14" r:id="rId11" xr:uid="{611232CF-2BCF-4E0D-BBD7-69920F8E78F0}"/>
+    <hyperlink ref="M15" r:id="rId12" xr:uid="{21B93587-1928-4FE5-B009-9BCA6437A144}"/>
+    <hyperlink ref="M16" r:id="rId13" xr:uid="{B0136BF8-669F-44FF-910A-02F1F5F76137}"/>
+    <hyperlink ref="M17" r:id="rId14" xr:uid="{7CDF109B-C27E-42DA-8F6B-27DA37910CA3}"/>
+    <hyperlink ref="M18" r:id="rId15" xr:uid="{AF38296B-D34D-4B62-A95E-E803839BB8D0}"/>
+    <hyperlink ref="M19" r:id="rId16" xr:uid="{71961F43-5AC1-4D4C-9947-BDA2F4612A45}"/>
+    <hyperlink ref="M20" r:id="rId17" xr:uid="{0B4A166C-FA48-48F6-ACA1-418301FCA438}"/>
+    <hyperlink ref="M21" r:id="rId18" xr:uid="{618C7455-9118-4DF9-8B39-3F3AB11D52FD}"/>
+    <hyperlink ref="M22" r:id="rId19" xr:uid="{B91560DC-2214-46EE-929C-8611F4859058}"/>
+    <hyperlink ref="M23" r:id="rId20" xr:uid="{2D7330C1-DB4D-47F6-9BDB-0E7930666DFB}"/>
+    <hyperlink ref="M24" r:id="rId21" xr:uid="{1F5C8F96-B89B-40BE-AB4B-82C03A6349D6}"/>
+    <hyperlink ref="M25" r:id="rId22" xr:uid="{3B90A023-9D9A-419A-9B0A-BCC0EBF0E891}"/>
+    <hyperlink ref="M26" r:id="rId23" xr:uid="{D2DD09B6-27F6-443F-87D5-B61231C4D0B8}"/>
+    <hyperlink ref="M27" r:id="rId24" xr:uid="{797B899D-F28F-4F4A-B1A4-7583FE909722}"/>
+    <hyperlink ref="N32" r:id="rId25" xr:uid="{92A31501-4E86-4A16-ABA9-1B82D10F12E5}"/>
+    <hyperlink ref="N33" r:id="rId26" xr:uid="{B5839527-8ACD-460E-9A79-82526D2B18EC}"/>
+    <hyperlink ref="N34" r:id="rId27" xr:uid="{6D2CE56C-F4A0-49AF-8384-BBA42285698B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z999"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -30152,1045 +29992,791 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57244DA5-AD15-4A43-8240-AEBCA378D9C2}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" customWidth="1"/>
-    <col min="2" max="26" width="8.5703125" customWidth="1"/>
+    <col min="1" max="1" width="88.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="88.5703125" style="18" customWidth="1"/>
+    <col min="4" max="4" width="51.85546875" style="18" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="19">
+        <v>2007</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="21">
+        <v>2009</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="20">
+        <v>2009</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="20">
+        <v>2010</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="20">
+        <v>2010</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="20">
+        <v>2010</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" s="20">
+        <v>2008</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B9" s="20">
+        <v>2007</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+    </row>
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+    </row>
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+    </row>
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+    </row>
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+    </row>
+    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
-    <hyperlink ref="B7" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{ADB9CD3C-1E44-43DD-99CA-A55DAF79BD0C}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{B562F1DF-7E13-4B87-B256-AAF309F9C316}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{9213B543-62B6-446E-A9BE-D29D1A55A603}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{4000D0B7-305E-4ADC-A978-C9D2A51D2C7F}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E79F85D-0A90-4BD9-B6A4-D426E9009D4C}">
-  <dimension ref="A1"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DECC613-DEAA-47C9-A408-516F751E59A8}">
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="13"/>
+    <col min="2" max="2" width="12.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="13">
+        <v>68.569999999999993</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.76</v>
+      </c>
+      <c r="E2" s="13">
+        <v>97.14</v>
+      </c>
+      <c r="F2" s="13">
+        <v>60</v>
+      </c>
+      <c r="G2" s="13">
+        <v>2.86</v>
+      </c>
+      <c r="H2" s="13">
+        <v>40</v>
+      </c>
+      <c r="I2" s="13">
+        <v>162.27000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="13">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="D3" s="13">
+        <v>0.76</v>
+      </c>
+      <c r="E3" s="13">
+        <v>91.43</v>
+      </c>
+      <c r="F3" s="13">
+        <v>48.57</v>
+      </c>
+      <c r="G3" s="13">
+        <v>8.57</v>
+      </c>
+      <c r="H3" s="13">
+        <v>51.43</v>
+      </c>
+      <c r="I3" s="13">
+        <v>162.81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="13">
+        <v>72.86</v>
+      </c>
+      <c r="D4" s="13">
+        <v>0.78</v>
+      </c>
+      <c r="E4" s="13">
+        <v>97.14</v>
+      </c>
+      <c r="F4" s="13">
+        <v>51.43</v>
+      </c>
+      <c r="G4" s="13">
+        <v>2.86</v>
+      </c>
+      <c r="H4" s="13">
+        <v>48.57</v>
+      </c>
+      <c r="I4" s="13">
+        <v>159.65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="13">
+        <v>60</v>
+      </c>
+      <c r="D5" s="13">
+        <v>0.71</v>
+      </c>
+      <c r="E5" s="13">
+        <v>100</v>
+      </c>
+      <c r="F5" s="13">
+        <v>80</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0</v>
+      </c>
+      <c r="H5" s="13">
+        <v>20</v>
+      </c>
+      <c r="I5" s="13">
+        <v>59.34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="13">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="D6" s="13">
+        <v>0.77</v>
+      </c>
+      <c r="E6" s="13">
+        <v>97.14</v>
+      </c>
+      <c r="F6" s="13">
+        <v>54.29</v>
+      </c>
+      <c r="G6" s="13">
+        <v>2.86</v>
+      </c>
+      <c r="H6" s="13">
+        <v>45.71</v>
+      </c>
+      <c r="I6" s="13">
+        <v>59.36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="13">
+        <v>65.709999999999994</v>
+      </c>
+      <c r="D7" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="E7" s="13">
+        <v>100</v>
+      </c>
+      <c r="F7" s="13">
+        <v>68.569999999999993</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
+        <v>31.43</v>
+      </c>
+      <c r="I7" s="13">
+        <v>59.44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="13">
+        <v>54</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="13">
+        <v>46</v>
+      </c>
+      <c r="F8" s="13">
+        <v>38</v>
+      </c>
+      <c r="G8" s="13">
+        <v>54</v>
+      </c>
+      <c r="H8" s="13">
+        <v>62</v>
+      </c>
+      <c r="I8" s="13">
+        <v>32.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="13">
+        <v>35</v>
+      </c>
+      <c r="D9" s="13">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13">
+        <v>30</v>
+      </c>
+      <c r="G9" s="13">
+        <v>100</v>
+      </c>
+      <c r="H9" s="13">
+        <v>70</v>
+      </c>
+      <c r="I9" s="13">
+        <v>23.66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="13">
+        <v>91.94</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0.95</v>
+      </c>
+      <c r="E10" s="13">
+        <v>100</v>
+      </c>
+      <c r="F10" s="13">
+        <v>31.25</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13">
+        <v>68.75</v>
+      </c>
+      <c r="I10" s="13">
+        <v>138.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="13">
+        <v>95.16</v>
+      </c>
+      <c r="D11" s="13">
+        <v>0.97</v>
+      </c>
+      <c r="E11" s="13">
+        <v>97.83</v>
+      </c>
+      <c r="F11" s="13">
+        <v>12.5</v>
+      </c>
+      <c r="G11" s="13">
+        <v>2.17</v>
+      </c>
+      <c r="H11" s="13">
+        <v>87.5</v>
+      </c>
+      <c r="I11" s="13">
+        <v>137.74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="13">
+        <v>90.32</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0.94</v>
+      </c>
+      <c r="E12" s="13">
+        <v>95.65</v>
+      </c>
+      <c r="F12" s="13">
+        <v>25</v>
+      </c>
+      <c r="G12" s="13">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H12" s="13">
+        <v>75</v>
+      </c>
+      <c r="I12" s="13">
+        <v>138.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="13">
+        <v>93.55</v>
+      </c>
+      <c r="D13" s="13">
+        <v>0.96</v>
+      </c>
+      <c r="E13" s="13">
+        <v>100</v>
+      </c>
+      <c r="F13" s="13">
+        <v>25</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
+        <v>75</v>
+      </c>
+      <c r="I13" s="13">
+        <v>55.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="13">
+        <v>95.16</v>
+      </c>
+      <c r="D14" s="13">
+        <v>0.97</v>
+      </c>
+      <c r="E14" s="13">
+        <v>97.83</v>
+      </c>
+      <c r="F14" s="13">
+        <v>12.5</v>
+      </c>
+      <c r="G14" s="13">
+        <v>2.17</v>
+      </c>
+      <c r="H14" s="13">
+        <v>87.5</v>
+      </c>
+      <c r="I14" s="13">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="13">
+        <v>93.55</v>
+      </c>
+      <c r="D15" s="13">
+        <v>0.96</v>
+      </c>
+      <c r="E15" s="13">
+        <v>97.83</v>
+      </c>
+      <c r="F15" s="13">
+        <v>18.75</v>
+      </c>
+      <c r="G15" s="13">
+        <v>2.17</v>
+      </c>
+      <c r="H15" s="13">
+        <v>81.25</v>
+      </c>
+      <c r="I15" s="13">
+        <v>55.29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="13">
+        <v>87.1</v>
+      </c>
+      <c r="D16" s="13">
+        <v>0.92</v>
+      </c>
+      <c r="E16" s="13">
+        <v>95.65</v>
+      </c>
+      <c r="F16" s="13">
+        <v>37.5</v>
+      </c>
+      <c r="G16" s="13">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H16" s="13">
+        <v>62.5</v>
+      </c>
+      <c r="I16" s="13">
+        <v>32.909999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="13">
+        <v>93.55</v>
+      </c>
+      <c r="D17" s="13">
+        <v>0.96</v>
+      </c>
+      <c r="E17" s="13">
+        <v>95.65</v>
+      </c>
+      <c r="F17" s="13">
+        <v>12.5</v>
+      </c>
+      <c r="G17" s="13">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H17" s="13">
+        <v>87.5</v>
+      </c>
+      <c r="I17" s="13">
+        <v>27.9</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/sheets/zzpaper2.xlsx
+++ b/docs/sheets/zzpaper2.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SyncData\paper2_main\docs\sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7833753-BED3-48C4-A582-11160277A5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0A6D25-8057-497E-8786-8045D4B83D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17010" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="16440" windowHeight="28440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dataset" sheetId="7" r:id="rId1"/>
     <sheet name="baseline" sheetId="1" r:id="rId2"/>
     <sheet name="idea_list" sheetId="10" r:id="rId3"/>
     <sheet name="perf_DFire" sheetId="9" r:id="rId4"/>
+    <sheet name="pipeline_speed" sheetId="11" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -140,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="157">
   <si>
     <t>citekey</t>
   </si>
@@ -662,16 +663,45 @@
   <si>
     <t>rule-based</t>
   </si>
+  <si>
+    <t>Normal_Pile</t>
+  </si>
+  <si>
+    <t>Skip_module_pile</t>
+  </si>
+  <si>
+    <t>Big Step</t>
+  </si>
+  <si>
+    <t>BIG_DL_infer</t>
+  </si>
+  <si>
+    <t>data_preprocess</t>
+  </si>
+  <si>
+    <t>infer</t>
+  </si>
+  <si>
+    <t>avg_FPS 
+(FullHD in video)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -814,68 +844,75 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="5" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{7317EE94-6EA5-49B6-9EB3-3A1D4149183D}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{A9F65691-4FC3-4A70-9633-38E217A6D207}"/>
     <cellStyle name="Normal 3" xfId="4" xr:uid="{15BA3769-005B-4CDF-B761-EEA81D658B44}"/>
+    <cellStyle name="Normal 4" xfId="5" xr:uid="{C2771873-93CF-4B05-A06A-D47C9D76DE5A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -972,6 +1009,55 @@
         <a:xfrm>
           <a:off x="6010275" y="6638925"/>
           <a:ext cx="5609524" cy="9142857"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>840442</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>121543</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA4441D2-D640-4BA8-969A-721552144C22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6477001"/>
+          <a:ext cx="6231592" cy="9265542"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -30779,4 +30865,198 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B4DD6E7-64C4-45E1-9F65-E92004400A2D}">
+  <dimension ref="A2:D27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" style="26" customWidth="1"/>
+    <col min="3" max="3" width="32" style="26" customWidth="1"/>
+    <col min="4" max="4" width="36.28515625" style="26" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="26"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="25"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="25">
+        <v>20.9</v>
+      </c>
+      <c r="D18" s="25"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="25"/>
+      <c r="B19" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="25">
+        <v>54.7</v>
+      </c>
+      <c r="D19" s="25"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+    </row>
+    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25">
+        <v>27.51</v>
+      </c>
+      <c r="D27" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>